--- a/resources/etsy/files/etsy-adv-ad-discipline.xlsx
+++ b/resources/etsy/files/etsy-adv-ad-discipline.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -498,7 +498,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -513,7 +512,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>20.67</v>
+        <v>21.27</v>
       </c>
     </row>
     <row r="6">
@@ -558,7 +557,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -576,7 +574,6 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -625,7 +622,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -637,7 +633,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
@@ -683,7 +678,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>judge. Over the ceiling = stop, not 'optimise for another month'.</t>
+          <t>judge. Over the ceiling = stop, not 'optimize for another month'.</t>
         </is>
       </c>
     </row>
@@ -760,11 +755,10 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>The 20.67 / 9.00 seed numbers are the book's illustration - use yours.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
+          <t>The 21.27 / 9.00 seed numbers are the book's illustration - use yours.</t>
+        </is>
+      </c>
+    </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>

--- a/resources/etsy/files/etsy-adv-ad-discipline.xlsx
+++ b/resources/etsy/files/etsy-adv-ad-discipline.xlsx
@@ -769,7 +769,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
